--- a/artfynd/A 36809-2025 artfynd.xlsx
+++ b/artfynd/A 36809-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136861304</v>
       </c>
       <c r="B2" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136861305</v>
       </c>
       <c r="B3" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36809-2025 artfynd.xlsx
+++ b/artfynd/A 36809-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136861304</v>
       </c>
       <c r="B2" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136861305</v>
       </c>
       <c r="B3" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36809-2025 artfynd.xlsx
+++ b/artfynd/A 36809-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136861304</v>
       </c>
       <c r="B2" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136861305</v>
       </c>
       <c r="B3" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36809-2025 artfynd.xlsx
+++ b/artfynd/A 36809-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136861304</v>
       </c>
       <c r="B2" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136861305</v>
       </c>
       <c r="B3" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36809-2025 artfynd.xlsx
+++ b/artfynd/A 36809-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136861304</v>
       </c>
       <c r="B2" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136861305</v>
       </c>
       <c r="B3" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36809-2025 artfynd.xlsx
+++ b/artfynd/A 36809-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136861304</v>
       </c>
       <c r="B2" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136861305</v>
       </c>
       <c r="B3" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36809-2025 artfynd.xlsx
+++ b/artfynd/A 36809-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136861304</v>
       </c>
       <c r="B2" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136861305</v>
       </c>
       <c r="B3" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36809-2025 artfynd.xlsx
+++ b/artfynd/A 36809-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136861304</v>
       </c>
       <c r="B2" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136861305</v>
       </c>
       <c r="B3" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36809-2025 artfynd.xlsx
+++ b/artfynd/A 36809-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136861304</v>
       </c>
       <c r="B2" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136861305</v>
       </c>
       <c r="B3" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36809-2025 artfynd.xlsx
+++ b/artfynd/A 36809-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136861304</v>
       </c>
       <c r="B2" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136861305</v>
       </c>
       <c r="B3" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36809-2025 artfynd.xlsx
+++ b/artfynd/A 36809-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136861304</v>
       </c>
       <c r="B2" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136861305</v>
       </c>
       <c r="B3" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
